--- a/src/result/lfw/result.xlsx
+++ b/src/result/lfw/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,33 +444,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>all_scores</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[0.6453202  0.57425743 0.65346535 0.62376238 0.60891089]</t>
-        </is>
+          <t>confidence_interval inf</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5646878586702819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>confidence_interval inf</t>
+          <t>confidence_interval sup</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5646878586702819</v>
+        <v>0.6775986359890365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>confidence_interval sup</t>
+          <t>score_1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6775986359890365</v>
+        <v>0.645320197044335</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>score_2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5742574257425742</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>score_3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6534653465346535</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>score_4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6237623762376238</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>score_5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6089108910891089</v>
       </c>
     </row>
   </sheetData>

--- a/src/result/lfw/result.xlsx
+++ b/src/result/lfw/result.xlsx
@@ -413,101 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="n">
+      <c r="A1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mean_accuracy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>0.8209530312637174</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>std_accuracy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>0.02190128720520227</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>confidence_interval inf</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>0.7771504568533129</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>confidence_interval sup</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="n">
         <v>0.864755605674122</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>score_1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" t="n">
         <v>0.8374384236453202</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>score_2</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" t="n">
         <v>0.7821782178217822</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>score_3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="n">
         <v>0.8415841584158416</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>score_4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="n">
         <v>0.8316831683168316</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>score_5</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" t="n">
         <v>0.8118811881188119</v>
       </c>
     </row>
